--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15000039.25</v>
+        <v>16710.57</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1469650</v>
+        <v>1637.24</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8709600.359999999</v>
+        <v>9702.799999999999</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8440274.560000001</v>
+        <v>9402.76</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12038495.53</v>
+        <v>13411.3</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>850533.9399999999</v>
+        <v>947.52</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>646000.48</v>
+        <v>719.67</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>28996817.41</v>
+        <v>32303.47</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10641900.7</v>
+        <v>11855.45</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3300000</v>
+        <v>3676.32</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>760001.24</v>
+        <v>846.67</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9433499.08</v>
+        <v>10509.25</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10770720.05</v>
+        <v>11998.96</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7213349.7</v>
+        <v>8035.92</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21849998.77</v>
+        <v>24341.66</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1471888.39</v>
+        <v>1639.74</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>292600.53</v>
+        <v>325.97</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5632044.73</v>
+        <v>6274.29</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4593265.6</v>
+        <v>5117.06</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>62485774.91</v>
+        <v>69611.34</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>51301787.03</v>
+        <v>57151.98</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>126279794.95</v>
+        <v>140680.11</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>19929099.52</v>
+        <v>22201.71</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4221001.84</v>
+        <v>4702.34</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20302500.27</v>
+        <v>22617.7</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>801039.52</v>
+        <v>892.39</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4522000</v>
+        <v>5037.67</v>
       </c>
     </row>
     <row r="29">
@@ -2216,11 +2216,11 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>106721703.76</v>
+        <v>118891.71</v>
       </c>
     </row>
     <row r="30">
@@ -2277,11 +2277,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1489601.06</v>
+        <v>1659.47</v>
       </c>
     </row>
     <row r="31">
@@ -2338,11 +2338,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15007719.87</v>
+        <v>16719.12</v>
       </c>
     </row>
     <row r="32">
@@ -2399,11 +2399,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>832199.49</v>
+        <v>927.1</v>
       </c>
     </row>
     <row r="33">
@@ -2460,11 +2460,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>594993.46</v>
+        <v>662.84</v>
       </c>
     </row>
     <row r="34">
@@ -2521,11 +2521,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12435500</v>
+        <v>13853.58</v>
       </c>
     </row>
     <row r="35">
@@ -2582,11 +2582,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3518799.95</v>
+        <v>3920.07</v>
       </c>
     </row>
     <row r="36">
@@ -2643,11 +2643,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2000985</v>
+        <v>2229.17</v>
       </c>
     </row>
     <row r="37">
@@ -2704,11 +2704,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13794000.37</v>
+        <v>15367</v>
       </c>
     </row>
     <row r="38">
@@ -2765,11 +2765,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5768399.99</v>
+        <v>6426.2</v>
       </c>
     </row>
     <row r="39">
@@ -2826,11 +2826,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>17599662.08</v>
+        <v>19606.64</v>
       </c>
     </row>
     <row r="40">
@@ -2887,11 +2887,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1116250.05</v>
+        <v>1243.54</v>
       </c>
     </row>
     <row r="41">
@@ -2948,11 +2948,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>350549.96</v>
+        <v>390.52</v>
       </c>
     </row>
     <row r="42">
@@ -3009,11 +3009,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1622601</v>
+        <v>1807.63</v>
       </c>
     </row>
     <row r="43">
@@ -3070,11 +3070,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>584249.1800000001</v>
+        <v>650.87</v>
       </c>
     </row>
     <row r="44">
@@ -3131,11 +3131,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>44010365</v>
+        <v>49029.09</v>
       </c>
     </row>
     <row r="45">
@@ -3192,11 +3192,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2202214</v>
+        <v>2453.34</v>
       </c>
     </row>
     <row r="46">
@@ -3253,11 +3253,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>538650.47</v>
+        <v>600.08</v>
       </c>
     </row>
     <row r="47">
@@ -3314,11 +3314,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3614208.5</v>
+        <v>4026.35</v>
       </c>
     </row>
     <row r="48">
@@ -3375,11 +3375,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1425600</v>
+        <v>1588.17</v>
       </c>
     </row>
     <row r="49">
@@ -3436,11 +3436,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1306800</v>
+        <v>1455.82</v>
       </c>
     </row>
     <row r="50">
@@ -3497,11 +3497,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>13000001.61</v>
+        <v>14482.46</v>
       </c>
     </row>
     <row r="51">
@@ -3558,11 +3558,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>15000000.81</v>
+        <v>16710.53</v>
       </c>
     </row>
     <row r="52">
@@ -3619,11 +3619,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>21374999.97</v>
+        <v>23812.5</v>
       </c>
     </row>
     <row r="53">
@@ -3680,11 +3680,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1681974.86</v>
+        <v>1873.78</v>
       </c>
     </row>
     <row r="54">
@@ -3741,11 +3741,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22610474.81</v>
+        <v>25188.86</v>
       </c>
     </row>
     <row r="55">
@@ -3802,11 +3802,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>69800000.26000001</v>
+        <v>77759.64</v>
       </c>
     </row>
     <row r="56">
@@ -3863,11 +3863,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>26800146.56</v>
+        <v>29856.3</v>
       </c>
     </row>
     <row r="57">
@@ -3924,11 +3924,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>382800</v>
+        <v>426.45</v>
       </c>
     </row>
     <row r="58">
@@ -3985,11 +3985,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>19071250.11</v>
+        <v>21246.04</v>
       </c>
     </row>
     <row r="59">
@@ -4046,11 +4046,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1983600.17</v>
+        <v>2209.8</v>
       </c>
     </row>
     <row r="60">
@@ -4107,11 +4107,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>14060480.7</v>
+        <v>15663.87</v>
       </c>
     </row>
     <row r="61">
@@ -4168,11 +4168,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>30030000.57</v>
+        <v>33454.47</v>
       </c>
     </row>
     <row r="62">
@@ -4229,11 +4229,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4295900</v>
+        <v>4785.78</v>
       </c>
     </row>
     <row r="63">
@@ -4290,11 +4290,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>24984050</v>
+        <v>27833.11</v>
       </c>
     </row>
     <row r="64">
@@ -4351,11 +4351,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1500000.53</v>
+        <v>1671.05</v>
       </c>
     </row>
     <row r="65">
@@ -4412,11 +4412,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>14820000.34</v>
+        <v>16510</v>
       </c>
     </row>
     <row r="66">
@@ -4473,11 +4473,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>29391696.53</v>
+        <v>32743.38</v>
       </c>
     </row>
     <row r="67">
@@ -4534,11 +4534,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>12005910</v>
+        <v>13375</v>
       </c>
     </row>
     <row r="68">
@@ -4595,11 +4595,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2565000.49</v>
+        <v>2857.5</v>
       </c>
     </row>
     <row r="69">
@@ -4656,11 +4656,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9369849.67</v>
+        <v>10438.34</v>
       </c>
     </row>
     <row r="70">
@@ -4717,11 +4717,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>814958.3199999999</v>
+        <v>907.89</v>
       </c>
     </row>
     <row r="71">
@@ -4778,11 +4778,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8399999.369999999</v>
+        <v>9357.889999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4839,11 +4839,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8667674.4</v>
+        <v>9656.09</v>
       </c>
     </row>
     <row r="73">
@@ -4900,11 +4900,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3495590.56</v>
+        <v>3894.21</v>
       </c>
     </row>
     <row r="74">
@@ -4961,11 +4961,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4822514.4</v>
+        <v>5372.45</v>
       </c>
     </row>
     <row r="75">
@@ -5022,11 +5022,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>16096800.61</v>
+        <v>17932.4</v>
       </c>
     </row>
     <row r="76">
@@ -5083,11 +5083,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>13206714.4</v>
+        <v>14712.74</v>
       </c>
     </row>
     <row r="77">
@@ -5144,11 +5144,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>31737410.55</v>
+        <v>35356.58</v>
       </c>
     </row>
     <row r="78">
@@ -5205,11 +5205,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3043800.03</v>
+        <v>3390.9</v>
       </c>
     </row>
     <row r="79">
@@ -5266,11 +5266,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>26028860.36</v>
+        <v>28997.06</v>
       </c>
     </row>
     <row r="80">
@@ -5327,11 +5327,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1198487.84</v>
+        <v>1335.16</v>
       </c>
     </row>
     <row r="81">
@@ -5388,11 +5388,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>19950000.2</v>
+        <v>22225</v>
       </c>
     </row>
     <row r="82">
@@ -5449,11 +5449,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1419134.74</v>
+        <v>1580.97</v>
       </c>
     </row>
     <row r="83">
@@ -5510,11 +5510,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1999999.2</v>
+        <v>2228.07</v>
       </c>
     </row>
     <row r="84">
@@ -5571,11 +5571,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>12596999.84</v>
+        <v>14033.5</v>
       </c>
     </row>
     <row r="85">
@@ -5632,11 +5632,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10294199.6</v>
+        <v>11468.1</v>
       </c>
     </row>
     <row r="86">
@@ -5693,11 +5693,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>24145485.8</v>
+        <v>26898.92</v>
       </c>
     </row>
     <row r="87">
@@ -5754,11 +5754,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>8854000.26</v>
+        <v>9863.67</v>
       </c>
     </row>
     <row r="88">
@@ -5815,11 +5815,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1023149.98</v>
+        <v>1139.82</v>
       </c>
     </row>
     <row r="89">
@@ -5876,11 +5876,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5293322.32</v>
+        <v>5896.95</v>
       </c>
     </row>
     <row r="90">
@@ -5937,11 +5937,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2109950.5</v>
+        <v>2350.56</v>
       </c>
     </row>
     <row r="91">
@@ -5998,11 +5998,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>41998075</v>
+        <v>46787.32</v>
       </c>
     </row>
     <row r="92">
@@ -6059,11 +6059,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7432800.1</v>
+        <v>8280.4</v>
       </c>
     </row>
     <row r="93">
@@ -6120,11 +6120,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>10187148.4</v>
+        <v>11348.84</v>
       </c>
     </row>
     <row r="94">
@@ -6181,11 +6181,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>300000.79</v>
+        <v>334.21</v>
       </c>
     </row>
     <row r="95">
@@ -6242,11 +6242,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>21519399.87</v>
+        <v>23973.36</v>
       </c>
     </row>
     <row r="96">
@@ -6303,11 +6303,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>11305000</v>
+        <v>12594.17</v>
       </c>
     </row>
     <row r="97">
@@ -6364,11 +6364,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3500000.05997686</v>
+        <v>3899.12</v>
       </c>
     </row>
     <row r="98">
@@ -6425,11 +6425,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2402278.59</v>
+        <v>2676.22</v>
       </c>
     </row>
     <row r="99">
@@ -6486,11 +6486,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1915200.4</v>
+        <v>2133.6</v>
       </c>
     </row>
     <row r="100">
@@ -6547,11 +6547,11 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>636134.4</v>
+        <v>708.6799999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6608,11 +6608,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2351425.12</v>
+        <v>2619.57</v>
       </c>
     </row>
     <row r="102">
@@ -6669,11 +6669,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8930950</v>
+        <v>9949.389999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6730,11 +6730,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>34849847.12</v>
+        <v>38823.95</v>
       </c>
     </row>
     <row r="104">
@@ -6791,11 +6791,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>999913.6800000001</v>
+        <v>1113.94</v>
       </c>
     </row>
     <row r="105">
@@ -6852,11 +6852,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>18398838.89</v>
+        <v>20496.95</v>
       </c>
     </row>
     <row r="106">
@@ -6913,11 +6913,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3419999.91</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="107">
@@ -6974,11 +6974,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>21443399.74</v>
+        <v>23888.7</v>
       </c>
     </row>
     <row r="108">
@@ -7035,11 +7035,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>39557049.66</v>
+        <v>44067.94</v>
       </c>
     </row>
     <row r="109">
@@ -7096,11 +7096,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>188100.5</v>
+        <v>209.55</v>
       </c>
     </row>
     <row r="110">
@@ -7157,11 +7157,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>46103703.94</v>
+        <v>51361.14</v>
       </c>
     </row>
     <row r="111">
@@ -7218,11 +7218,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>999999.6</v>
+        <v>1114.03</v>
       </c>
     </row>
     <row r="112">
@@ -7279,11 +7279,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5656775.55</v>
+        <v>6301.85</v>
       </c>
     </row>
     <row r="113">
@@ -7340,11 +7340,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>16963199.98</v>
+        <v>18897.6</v>
       </c>
     </row>
     <row r="114">
@@ -7401,11 +7401,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>13589619.54</v>
+        <v>15139.31</v>
       </c>
     </row>
     <row r="115">
@@ -7462,11 +7462,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>13662899.68</v>
+        <v>15220.95</v>
       </c>
     </row>
     <row r="116">
@@ -7523,11 +7523,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>540000.28</v>
+        <v>601.58</v>
       </c>
     </row>
     <row r="117">
@@ -7584,11 +7584,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8728599.539999999</v>
+        <v>9723.969999999999</v>
       </c>
     </row>
     <row r="118">
@@ -7645,11 +7645,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>35890525.01</v>
+        <v>39983.3</v>
       </c>
     </row>
     <row r="119">
@@ -7706,11 +7706,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3999996</v>
+        <v>4456.14</v>
       </c>
     </row>
     <row r="120">
@@ -7767,11 +7767,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>398999.8</v>
+        <v>444.5</v>
       </c>
     </row>
     <row r="121">
@@ -7828,11 +7828,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1003200.05</v>
+        <v>1117.6</v>
       </c>
     </row>
     <row r="122">
@@ -7889,11 +7889,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8606999.57</v>
+        <v>9588.5</v>
       </c>
     </row>
     <row r="123">
@@ -7950,11 +7950,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>300000.79</v>
+        <v>334.21</v>
       </c>
     </row>
     <row r="124">
@@ -8011,11 +8011,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9805899.34</v>
+        <v>10924.11</v>
       </c>
     </row>
     <row r="125">
@@ -8072,11 +8072,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2281900.68</v>
+        <v>2542.12</v>
       </c>
     </row>
     <row r="126">
@@ -8133,11 +8133,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>17000000.02</v>
+        <v>18938.59</v>
       </c>
     </row>
     <row r="127">
@@ -8194,11 +8194,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6783000</v>
+        <v>7556.5</v>
       </c>
     </row>
     <row r="128">
@@ -8255,11 +8255,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>57981000.34</v>
+        <v>64592.86</v>
       </c>
     </row>
     <row r="129">
@@ -8316,11 +8316,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>904400</v>
+        <v>1007.53</v>
       </c>
     </row>
     <row r="130">
@@ -8377,11 +8377,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5084400.01</v>
+        <v>5664.2</v>
       </c>
     </row>
     <row r="131">
@@ -8438,11 +8438,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>8999999.810000001</v>
+        <v>10026.31</v>
       </c>
     </row>
     <row r="132">
@@ -8499,11 +8499,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>39086800.1</v>
+        <v>43544.06</v>
       </c>
     </row>
     <row r="133">
@@ -8560,11 +8560,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>11256789.83</v>
+        <v>12540.46</v>
       </c>
     </row>
     <row r="134">
@@ -8621,11 +8621,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2727449.95</v>
+        <v>3038.47</v>
       </c>
     </row>
     <row r="135">
@@ -8682,11 +8682,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1500000.53</v>
+        <v>1671.05</v>
       </c>
     </row>
     <row r="136">
@@ -8743,11 +8743,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>12043624.61</v>
+        <v>13417.02</v>
       </c>
     </row>
     <row r="137">
@@ -8804,11 +8804,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>886308.61</v>
+        <v>987.38</v>
       </c>
     </row>
     <row r="138">
@@ -8865,11 +8865,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>7917299.61</v>
+        <v>8820.15</v>
       </c>
     </row>
     <row r="139">
@@ -8926,11 +8926,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1399999.9</v>
+        <v>1559.65</v>
       </c>
     </row>
     <row r="140">
@@ -8987,11 +8987,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>11912999.86</v>
+        <v>13271.5</v>
       </c>
     </row>
     <row r="141">
@@ -9048,11 +9048,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>28534199.85</v>
+        <v>31788.1</v>
       </c>
     </row>
     <row r="142">
@@ -9109,11 +9109,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>41062799.91</v>
+        <v>45745.39</v>
       </c>
     </row>
     <row r="143">
@@ -9170,11 +9170,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>109999.91</v>
+        <v>122.54</v>
       </c>
     </row>
     <row r="144">
@@ -9231,11 +9231,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>61999997.93</v>
+        <v>69070.17</v>
       </c>
     </row>
     <row r="145">
@@ -9292,11 +9292,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>141300</v>
+        <v>157.41</v>
       </c>
     </row>
     <row r="146">
@@ -9353,11 +9353,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2349026.38</v>
+        <v>2616.9</v>
       </c>
     </row>
     <row r="147">
@@ -9414,11 +9414,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1611806.98</v>
+        <v>1795.61</v>
       </c>
     </row>
     <row r="148">
@@ -9475,11 +9475,11 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>16565149.8</v>
+        <v>18454.16</v>
       </c>
     </row>
     <row r="149">
@@ -9536,11 +9536,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4793952.24</v>
+        <v>5340.63</v>
       </c>
     </row>
     <row r="150">
@@ -9597,11 +9597,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>11217599.91</v>
+        <v>12496.8</v>
       </c>
     </row>
     <row r="151">
@@ -9658,11 +9658,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>12708150.6</v>
+        <v>14157.32</v>
       </c>
     </row>
     <row r="152">
@@ -9719,11 +9719,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>10544999.9</v>
+        <v>11747.5</v>
       </c>
     </row>
     <row r="153">
@@ -9780,11 +9780,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>53048000.29</v>
+        <v>59097.33</v>
       </c>
     </row>
     <row r="154">
@@ -9841,11 +9841,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>963600</v>
+        <v>1073.48</v>
       </c>
     </row>
     <row r="155">
@@ -9902,11 +9902,11 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>14000150.44</v>
+        <v>15596.66</v>
       </c>
     </row>
     <row r="156">
@@ -9963,11 +9963,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3007130</v>
+        <v>3350.05</v>
       </c>
     </row>
     <row r="157">
@@ -10024,11 +10024,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4717000.64</v>
+        <v>5254.9</v>
       </c>
     </row>
     <row r="158">
@@ -10085,11 +10085,11 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>45477900.16</v>
+        <v>50663.97</v>
       </c>
     </row>
     <row r="159">
@@ -10146,11 +10146,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1235000.03</v>
+        <v>1375.83</v>
       </c>
     </row>
     <row r="160">
@@ -10207,11 +10207,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>24665799.55</v>
+        <v>27478.56</v>
       </c>
     </row>
     <row r="161">
@@ -10268,11 +10268,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>53961000</v>
+        <v>60114.44</v>
       </c>
     </row>
     <row r="162">
@@ -10329,11 +10329,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>220000.95</v>
+        <v>245.09</v>
       </c>
     </row>
     <row r="163">
@@ -10390,11 +10390,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>15331290.45</v>
+        <v>17079.59</v>
       </c>
     </row>
     <row r="164">
@@ -10451,11 +10451,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>11466401.76</v>
+        <v>12773.97</v>
       </c>
     </row>
     <row r="165">
@@ -10512,11 +10512,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1500000.29004628</v>
+        <v>1671.05</v>
       </c>
     </row>
     <row r="166">
@@ -10573,11 +10573,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>799999.46</v>
+        <v>891.23</v>
       </c>
     </row>
     <row r="167">
@@ -10634,11 +10634,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10463908</v>
+        <v>11657.16</v>
       </c>
     </row>
     <row r="168">
@@ -10695,11 +10695,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>351999.26</v>
+        <v>392.14</v>
       </c>
     </row>
     <row r="169">
@@ -10756,11 +10756,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>5878600</v>
+        <v>6548.97</v>
       </c>
     </row>
     <row r="170">
@@ -10817,11 +10817,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>49999.84</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="171">
@@ -10878,11 +10878,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>40065299.85</v>
+        <v>44634.14</v>
       </c>
     </row>
     <row r="172">
@@ -10939,11 +10939,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>99999.67999999999</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="173">
@@ -11000,11 +11000,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>981539.67</v>
+        <v>1093.47</v>
       </c>
     </row>
     <row r="174">
@@ -11061,11 +11061,11 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>66000775.26</v>
+        <v>73527.17</v>
       </c>
     </row>
     <row r="175">
@@ -11122,11 +11122,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>416954.4</v>
+        <v>464.5</v>
       </c>
     </row>
     <row r="176">
@@ -11183,11 +11183,11 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>499999.8</v>
+        <v>557.02</v>
       </c>
     </row>
     <row r="177">
@@ -11244,11 +11244,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>900000.09</v>
+        <v>1002.63</v>
       </c>
     </row>
     <row r="178">
@@ -11305,11 +11305,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2500000.14</v>
+        <v>2785.09</v>
       </c>
     </row>
     <row r="179">
@@ -11366,11 +11366,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2872600.5</v>
+        <v>3200.18</v>
       </c>
     </row>
     <row r="180">
@@ -11427,11 +11427,11 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3614208.5</v>
+        <v>4026.35</v>
       </c>
     </row>
     <row r="181">
@@ -11488,11 +11488,11 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>12200356</v>
+        <v>13591.62</v>
       </c>
     </row>
     <row r="182">
@@ -11549,11 +11549,11 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>11254650.88</v>
+        <v>12538.07</v>
       </c>
     </row>
     <row r="183">
@@ -11610,11 +11610,11 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>30000000.5</v>
+        <v>33421.05</v>
       </c>
     </row>
     <row r="184">
@@ -11671,11 +11671,11 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>35000000.77</v>
+        <v>38991.22</v>
       </c>
     </row>
     <row r="185">
@@ -11732,11 +11732,11 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>557158.8</v>
+        <v>620.6900000000001</v>
       </c>
     </row>
     <row r="186">
@@ -11797,11 +11797,11 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>222358883.95</v>
+        <v>247715.57</v>
       </c>
     </row>
     <row r="187">
@@ -11862,11 +11862,11 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1028953968</v>
+        <v>1146290.69</v>
       </c>
     </row>
     <row r="188">
@@ -11923,11 +11923,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>17102612.11</v>
+        <v>19052.91</v>
       </c>
     </row>
     <row r="189">
@@ -11984,11 +11984,11 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>780424.85</v>
+        <v>869.42</v>
       </c>
     </row>
     <row r="190">
@@ -12045,11 +12045,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>17646500.08</v>
+        <v>19658.82</v>
       </c>
     </row>
     <row r="191">
@@ -12106,11 +12106,11 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4989361.52</v>
+        <v>5558.32</v>
       </c>
     </row>
     <row r="192">
@@ -12167,11 +12167,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>50478249.43</v>
+        <v>56234.53</v>
       </c>
     </row>
     <row r="193">
@@ -12228,11 +12228,11 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>18000000.75</v>
+        <v>20052.63</v>
       </c>
     </row>
     <row r="194">
@@ -12289,11 +12289,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4634640</v>
+        <v>5163.15</v>
       </c>
     </row>
     <row r="195">
@@ -12350,11 +12350,11 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>559597.5</v>
+        <v>623.41</v>
       </c>
     </row>
     <row r="196">
@@ -12411,11 +12411,11 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5475378.48</v>
+        <v>6099.76</v>
       </c>
     </row>
     <row r="197">
@@ -12472,11 +12472,11 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>17526003.44</v>
+        <v>19524.58</v>
       </c>
     </row>
     <row r="198">
@@ -12533,11 +12533,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2464000</v>
+        <v>2744.98</v>
       </c>
     </row>
     <row r="199">
@@ -12594,11 +12594,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1320000</v>
+        <v>1470.53</v>
       </c>
     </row>
     <row r="200">
@@ -12655,11 +12655,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>200000.24</v>
+        <v>222.81</v>
       </c>
     </row>
     <row r="201">
@@ -12716,11 +12716,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>34927698.51</v>
+        <v>38910.68</v>
       </c>
     </row>
     <row r="202">
@@ -12777,11 +12777,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>45657950.05</v>
+        <v>50864.55</v>
       </c>
     </row>
     <row r="203">
@@ -12838,11 +12838,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>455999.61</v>
+        <v>508</v>
       </c>
     </row>
     <row r="204">
@@ -12899,11 +12899,11 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>10496550.06</v>
+        <v>11693.52</v>
       </c>
     </row>
     <row r="205">
@@ -12960,11 +12960,11 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>52249999.55</v>
+        <v>58208.33</v>
       </c>
     </row>
     <row r="206">
@@ -13021,11 +13021,11 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>299999.92</v>
+        <v>334.21</v>
       </c>
     </row>
     <row r="207">
@@ -13082,11 +13082,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1800000.19</v>
+        <v>2005.26</v>
       </c>
     </row>
     <row r="208">
@@ -13143,11 +13143,11 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>15035650</v>
+        <v>16750.24</v>
       </c>
     </row>
     <row r="209">
@@ -13204,11 +13204,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>264000</v>
+        <v>294.11</v>
       </c>
     </row>
     <row r="210">
@@ -13265,11 +13265,11 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>264000.01</v>
+        <v>294.11</v>
       </c>
     </row>
     <row r="211">
@@ -13326,11 +13326,11 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>33201001.07</v>
+        <v>36987.08</v>
       </c>
     </row>
     <row r="212">
@@ -13387,11 +13387,11 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>69740545</v>
+        <v>77693.41</v>
       </c>
     </row>
     <row r="213">
@@ -13448,11 +13448,11 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>120000.32</v>
+        <v>133.68</v>
       </c>
     </row>
     <row r="214">
@@ -13509,11 +13509,11 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1995000.13</v>
+        <v>2222.5</v>
       </c>
     </row>
     <row r="215">
@@ -13570,11 +13570,11 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>12350000.29</v>
+        <v>13758.33</v>
       </c>
     </row>
     <row r="216">
@@ -13631,11 +13631,11 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>343482.08</v>
+        <v>382.65</v>
       </c>
     </row>
     <row r="217">
@@ -13692,11 +13692,11 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>11754657.51</v>
+        <v>13095.1</v>
       </c>
     </row>
     <row r="218">
@@ -13753,11 +13753,11 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>28577901.59</v>
+        <v>31836.78</v>
       </c>
     </row>
     <row r="219">
@@ -13814,11 +13814,11 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>61902000.54</v>
+        <v>68960.99000000001</v>
       </c>
     </row>
     <row r="220">
@@ -13875,11 +13875,11 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>62845349.66</v>
+        <v>70011.92</v>
       </c>
     </row>
     <row r="221">
@@ -13936,11 +13936,11 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>63879899.6</v>
+        <v>71164.44</v>
       </c>
     </row>
     <row r="222">
@@ -13997,11 +13997,11 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>40710349.58</v>
+        <v>45352.75</v>
       </c>
     </row>
     <row r="223">
@@ -14058,11 +14058,11 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>45271790.47</v>
+        <v>50434.36</v>
       </c>
     </row>
     <row r="224">
@@ -14119,11 +14119,11 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1995000.13</v>
+        <v>2222.5</v>
       </c>
     </row>
     <row r="225">
@@ -14180,11 +14180,11 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6500000.8</v>
+        <v>7241.23</v>
       </c>
     </row>
     <row r="226">
@@ -14241,11 +14241,11 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>27632000</v>
+        <v>30783.01</v>
       </c>
     </row>
     <row r="227">
@@ -14302,11 +14302,11 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>10909799.81</v>
+        <v>12153.9</v>
       </c>
     </row>
     <row r="228">
@@ -14363,11 +14363,11 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>34061015.38</v>
+        <v>37945.16</v>
       </c>
     </row>
     <row r="229">
@@ -14424,11 +14424,11 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>264000</v>
+        <v>294.11</v>
       </c>
     </row>
     <row r="230">
@@ -14485,11 +14485,11 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>697080</v>
+        <v>776.5700000000001</v>
       </c>
     </row>
     <row r="231">
@@ -14546,11 +14546,11 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>28925600</v>
+        <v>32224.13</v>
       </c>
     </row>
     <row r="232">
@@ -14607,11 +14607,11 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>21000168</v>
+        <v>23394.92</v>
       </c>
     </row>
     <row r="233">
@@ -14668,11 +14668,11 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>28499999.96</v>
+        <v>31750</v>
       </c>
     </row>
     <row r="234">
@@ -14729,11 +14729,11 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>26054700.2</v>
+        <v>29025.85</v>
       </c>
     </row>
     <row r="235">
@@ -14790,11 +14790,11 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>34016745</v>
+        <v>37895.84</v>
       </c>
     </row>
     <row r="236">
@@ -14851,11 +14851,11 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>44808365.73</v>
+        <v>49918.09</v>
       </c>
     </row>
     <row r="237">
@@ -14912,11 +14912,11 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>32794380.57</v>
+        <v>36534.09</v>
       </c>
     </row>
     <row r="238">
@@ -14973,11 +14973,11 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>51623976.13</v>
+        <v>57510.91</v>
       </c>
     </row>
     <row r="239">
@@ -15034,11 +15034,11 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>15290963.25</v>
+        <v>17034.67</v>
       </c>
     </row>
     <row r="240">
@@ -15095,11 +15095,11 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8486652.199999999</v>
+        <v>9454.43</v>
       </c>
     </row>
     <row r="241">
@@ -15156,11 +15156,11 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>42000000.24</v>
+        <v>46789.47</v>
       </c>
     </row>
     <row r="242">
@@ -15217,11 +15217,11 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1200000.88</v>
+        <v>1336.84</v>
       </c>
     </row>
     <row r="243">
@@ -15278,11 +15278,11 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>9219100.880000001</v>
+        <v>10270.4</v>
       </c>
     </row>
     <row r="244">
@@ -15339,11 +15339,11 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>21097125.33</v>
+        <v>23502.94</v>
       </c>
     </row>
     <row r="245">
@@ -15400,11 +15400,11 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>9404064.25</v>
+        <v>10476.46</v>
       </c>
     </row>
     <row r="246">
@@ -15461,11 +15461,11 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>57588876.24</v>
+        <v>64156.02</v>
       </c>
     </row>
     <row r="247">
@@ -15526,11 +15526,11 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>72064670.59992971</v>
+        <v>80282.56</v>
       </c>
     </row>
     <row r="248">
@@ -15587,11 +15587,11 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>13000000.48</v>
+        <v>14482.45</v>
       </c>
     </row>
     <row r="249">
@@ -15648,11 +15648,11 @@
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>65214660</v>
+        <v>72651.41</v>
       </c>
     </row>
     <row r="250">
@@ -15709,11 +15709,11 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4069800</v>
+        <v>4533.9</v>
       </c>
     </row>
     <row r="251">
@@ -15770,11 +15770,11 @@
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1899999.7</v>
+        <v>2116.67</v>
       </c>
     </row>
     <row r="252">
@@ -15831,11 +15831,11 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>8515087.66</v>
+        <v>9486.110000000001</v>
       </c>
     </row>
     <row r="253">
@@ -15892,11 +15892,11 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1170000.8</v>
+        <v>1303.42</v>
       </c>
     </row>
     <row r="254">
@@ -15957,11 +15957,11 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>74483200</v>
+        <v>82976.89</v>
       </c>
     </row>
     <row r="255">
@@ -16018,11 +16018,11 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>33137651.24</v>
+        <v>36916.5</v>
       </c>
     </row>
     <row r="256">
@@ -16079,11 +16079,11 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>12350000.29</v>
+        <v>13758.33</v>
       </c>
     </row>
     <row r="257">
@@ -16140,11 +16140,11 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>188100.5</v>
+        <v>209.55</v>
       </c>
     </row>
     <row r="258">
@@ -16201,11 +16201,11 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>20000001.08</v>
+        <v>22280.7</v>
       </c>
     </row>
     <row r="259">
@@ -16262,11 +16262,11 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>14405704.88</v>
+        <v>16048.46</v>
       </c>
     </row>
     <row r="260">
@@ -16323,11 +16323,11 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>564476</v>
+        <v>628.85</v>
       </c>
     </row>
     <row r="261">
@@ -16384,11 +16384,11 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>15001735</v>
+        <v>16712.46</v>
       </c>
     </row>
     <row r="262">
@@ -16445,11 +16445,11 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1600000.16</v>
+        <v>1782.46</v>
       </c>
     </row>
     <row r="263">
@@ -16506,11 +16506,11 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>8083075</v>
+        <v>9004.83</v>
       </c>
     </row>
     <row r="264">
@@ -16567,11 +16567,11 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>582766.8</v>
+        <v>649.22</v>
       </c>
     </row>
     <row r="265">
@@ -16628,11 +16628,11 @@
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>55599700.45</v>
+        <v>61940.01</v>
       </c>
     </row>
     <row r="266">
@@ -16689,11 +16689,11 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>4797579.72</v>
+        <v>5344.67</v>
       </c>
     </row>
     <row r="267">
@@ -16750,11 +16750,11 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1817255.01</v>
+        <v>2024.49</v>
       </c>
     </row>
     <row r="268">
@@ -16811,11 +16811,11 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>70000000.40000001</v>
+        <v>77982.45</v>
       </c>
     </row>
     <row r="269">
@@ -16872,11 +16872,11 @@
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>28262500</v>
+        <v>31485.41</v>
       </c>
     </row>
   </sheetData>
